--- a/yahoo-dsp-pois/HYPR_JLR_POIs_Unificados_LIMPO.xlsx
+++ b/yahoo-dsp-pois/HYPR_JLR_POIs_Unificados_LIMPO.xlsx
@@ -44,7 +44,7 @@
     <font>
       <name val="Arial"/>
       <b val="1"/>
-      <color rgb="001F3864"/>
+      <color rgb="00C00000"/>
       <sz val="13"/>
     </font>
     <font>
@@ -523,7 +523,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B34"/>
+  <dimension ref="A1:B26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -533,7 +533,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>HYPR / JLR — POIs Unificados · versão corrigida para Yahoo DSP</t>
+          <t>HYPR / JLR — POIs Unificados · base limpa (NÃO é arquivo de upload)</t>
         </is>
       </c>
       <c r="B1" s="2" t="inlineStr"/>
@@ -545,36 +545,36 @@
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>PROBLEMA</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>O arquivo foi enviado no campo de upload por ENDEREÇO (geofencing address list).</t>
+          <t>SITUAÇÃO</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="inlineStr">
+        <is>
+          <t>Os CSVs de coordenadas deste pacote NÃO funcionam no geofencing da Yahoo DSP.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr"/>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>A DSP tentou geocodificar as colunas como endereço, em vez de ler as coordenadas.</t>
+      <c r="B4" s="5" t="inlineStr">
+        <is>
+          <t>A DSP exige ENDEREÇO em texto, não coordenada. Faltam os endereços dos POIs.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr"/>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>Prova 1: a própria linha de CABEÇALHO ('Latitude,Longitude,...') voltou como 'successful'</t>
-        </is>
-      </c>
+      <c r="B5" s="2" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="inlineStr"/>
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>FORMATO DA DSP</t>
+        </is>
+      </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>— a DSP geocodificou o texto do cabeçalho como se fosse um endereço.</t>
+          <t>· Arquivo TXT ou CSV, UM ENDEREÇO POR LINHA (texto livre, não é planilha).</t>
         </is>
       </c>
     </row>
@@ -582,7 +582,7 @@
       <c r="A7" s="3" t="inlineStr"/>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>Prova 2: o motivo do erro acompanha exatamente a coluna Estado:</t>
+          <t>· Máximo 10.000 endereços por line item e por arquivo.</t>
         </is>
       </c>
     </row>
@@ -590,7 +590,7 @@
       <c r="A8" s="3" t="inlineStr"/>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">        Estado = 'SP' (UF válida)  -&gt;  'Incomplete address'            1.030 linhas</t>
+          <t>· Caracteres especiais podem dar erro: é, à, ç, #, -</t>
         </is>
       </c>
     </row>
@@ -598,7 +598,7 @@
       <c r="A9" s="3" t="inlineStr"/>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">        Estado = 'Demais Praças'   -&gt;  'Unknown error'                 1.021 linhas</t>
+          <t>· Só Airports, Arena/Stadiums e Universities/Colleges podem ir só com o nome.</t>
         </is>
       </c>
     </row>
@@ -606,7 +606,7 @@
       <c r="A10" s="3" t="inlineStr"/>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">        Estado = 'Demais Praças'   -&gt;  'Cannot match full address'       119 linhas</t>
+          <t xml:space="preserve">  Todas as 11 categorias desta lista exigem endereço completo.</t>
         </is>
       </c>
     </row>
@@ -614,31 +614,31 @@
       <c r="A11" s="3" t="inlineStr"/>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>Os 3 'successful' foram coincidência de geocodificação, não acerto de coordenada.</t>
+          <t>· O raio é em MILHAS. O 0,3 da planilha = 483 m, não 300 m.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr"/>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>Outras 513 linhas foram descartadas em silêncio, sem nem aparecer no relatório.</t>
-        </is>
-      </c>
+      <c r="B12" s="2" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="3" t="inlineStr"/>
-      <c r="B13" s="2" t="inlineStr"/>
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>POR QUE FALHOU</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>Upload 1 (5 colunas):  3 de 2.686 aceitos.</t>
+        </is>
+      </c>
     </row>
     <row r="14">
-      <c r="A14" s="4" t="inlineStr">
-        <is>
-          <t>SOLUÇÃO</t>
-        </is>
-      </c>
+      <c r="A14" s="3" t="inlineStr"/>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>Subir os arquivos da pasta /upload no campo de LATITUDE/LONGITUDE da DSP.</t>
+          <t xml:space="preserve">  Cada linha virou uma string de endereço. Com 'SP' (UF válida) -&gt; 'Incomplete</t>
         </is>
       </c>
     </row>
@@ -646,23 +646,23 @@
       <c r="A15" s="3" t="inlineStr"/>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>Formato: 3 colunas (lat, lon, raio), SEM cabeçalho, sem acento, quebra de linha CRLF.</t>
+          <t xml:space="preserve">  address'; com 'Demais Praças' -&gt; 'Unknown error'. Os 3 aceitos foram coincidência.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="inlineStr"/>
-      <c r="B16" s="2" t="inlineStr"/>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>Upload 2 (3 colunas de coordenada):  0 de 2.424 aceitos.</t>
+        </is>
+      </c>
     </row>
     <row r="17">
-      <c r="A17" s="4" t="inlineStr">
-        <is>
-          <t>LIMPEZA APLICADA</t>
-        </is>
-      </c>
+      <c r="A17" s="3" t="inlineStr"/>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>1. Cabeçalho removido — a DSP lê a 1a linha como dado.</t>
+          <t xml:space="preserve">  Sem texto de endereço, '-23.568083,-46.673556,0.3' não geocodifica em nada.</t>
         </is>
       </c>
     </row>
@@ -670,7 +670,7 @@
       <c r="A18" s="3" t="inlineStr"/>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>2. Colunas 'Estado' e 'POI' retiradas do upload — viravam campos de endereço.</t>
+          <t>Prova: a linha de CABEÇALHO do arquivo original voltou como 'successful' — a DSP</t>
         </is>
       </c>
     </row>
@@ -678,23 +678,23 @@
       <c r="A19" s="3" t="inlineStr"/>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>3. Duplicatas removidas: 2,686 linhas originais -&gt; 2,424 geofences únicos.</t>
+          <t>geocodificou o texto do cabeçalho como se fosse endereço.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="inlineStr"/>
-      <c r="B20" s="2" t="inlineStr">
-        <is>
-          <t>4. Coordenadas arredondadas para 6 casas (~11 cm), eliminando ruído de float</t>
-        </is>
-      </c>
+      <c r="B20" s="2" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="3" t="inlineStr"/>
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>O QUE FALTA</t>
+        </is>
+      </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">        ex.: -46,72234770000001  -&gt;  -46,722348</t>
+          <t>1. Recuperar o export original dos POIs COM endereço (caminho limpo), ou</t>
         </is>
       </c>
     </row>
@@ -702,7 +702,7 @@
       <c r="A22" s="3" t="inlineStr"/>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>5. Validação: 100% das coordenadas são válidas e caem dentro do Brasil.</t>
+          <t>2. Geocodificação reversa das 2.424 coordenadas (aproximado).</t>
         </is>
       </c>
     </row>
@@ -713,92 +713,28 @@
     <row r="24">
       <c r="A24" s="4" t="inlineStr">
         <is>
-          <t>ATENÇÃO — RAIO</t>
-        </is>
-      </c>
-      <c r="B24" s="5" t="inlineStr">
-        <is>
-          <t>O valor 0,3 foi mantido como estava. Confirme a UNIDADE no painel da DSP:</t>
+          <t>ESTA PLANILHA</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>'POIs_Limpos' = 2.436 pares POI x coordenada. já deduplicados e validados</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="inlineStr"/>
-      <c r="B25" s="5" t="inlineStr">
-        <is>
-          <t>se a DSP interpretar em MILHAS, 0,3 = 483 m em vez dos 300 m pretendidos.</t>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>dentro do Brasil. 2.424 coordenadas distintas. Insumo para os dois caminhos acima.</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="inlineStr"/>
-      <c r="B26" s="2" t="inlineStr"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="4" t="inlineStr">
-        <is>
-          <t>2.436 x 2.424</t>
-        </is>
-      </c>
-      <c r="B27" s="2" t="inlineStr">
-        <is>
-          <t>A aba 'POIs_Limpos' tem 2.436 linhas e o arquivo único de upload tem 2.424.</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="3" t="inlineStr"/>
-      <c r="B28" s="2" t="inlineStr">
-        <is>
-          <t>A diferença são 12 coordenadas que pertencem a DUAS categorias (ex.: um clube</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="3" t="inlineStr"/>
-      <c r="B29" s="2" t="inlineStr">
-        <is>
-          <t>que também é golf club). Elas aparecem nos dois arquivos por POI — correto, são listas</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="3" t="inlineStr"/>
-      <c r="B30" s="2" t="inlineStr">
-        <is>
-          <t>de targeting separadas — mas só uma vez no arquivo único, que não aceita geofence repetido.</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="3" t="inlineStr"/>
-      <c r="B31" s="2" t="inlineStr"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="4" t="inlineStr">
-        <is>
-          <t>NESTE ARQUIVO</t>
-        </is>
-      </c>
-      <c r="B32" s="2" t="inlineStr">
-        <is>
-          <t>'POIs_Limpos' = base completa com Estado e POI (referência, não é o arquivo de upload).</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="3" t="inlineStr"/>
-      <c r="B33" s="2" t="inlineStr">
-        <is>
-          <t>'Resumo' = geofences por Estado e por categoria de POI.</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="3" t="inlineStr"/>
-      <c r="B34" s="2" t="inlineStr">
-        <is>
-          <t>Arquivos de upload prontos: /upload, /por_estado e /por_poi (CSV).</t>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>'Resumo' = contagem por Estado e por categoria.</t>
         </is>
       </c>
     </row>
